--- a/marks.xlsx
+++ b/marks.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SITNGP-ADMISSION-01\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7995"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Sr.No</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>RESULT</t>
+  </si>
+  <si>
+    <t>GRADE</t>
   </si>
 </sst>
 </file>
@@ -442,16 +445,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
     <col min="9" max="9" width="25.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
     <col min="11" max="11" width="43.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,8 +483,11 @@
       <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -511,8 +518,12 @@
         <f>IF(MIN(C2:F2)&gt;=50,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J2" t="str">
+        <f>IF(I2="FAIL","",IF(H2&gt;=90,"A+",IF(H2&gt;=80,"A",IF(H2&gt;=70,"B+",IF(H2&gt;=60,"B",IF(H2&gt;=55,"C",IF(H2&gt;=50,"D","F")))))))</f>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -543,8 +554,12 @@
         <f t="shared" ref="I3:I21" si="2">IF(MIN(C3:F3)&gt;=50,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J21" si="3">IF(H3&gt;=90,"A+",IF(H3&gt;=80,"A",IF(H3&gt;=70,"B+",IF(H3&gt;=60,"B",IF(H3&gt;=55,"C",IF(H3&gt;=50,"D","F"))))))</f>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -575,8 +590,12 @@
         <f t="shared" si="2"/>
         <v>FAIL</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J4" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -607,8 +626,12 @@
         <f t="shared" si="2"/>
         <v>FAIL</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J5" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -639,12 +662,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-      <c r="K6" t="e">
-        <f>MIN((C6:F6)&gt;90)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J6" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -675,8 +698,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J7" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -707,8 +734,12 @@
         <f t="shared" si="2"/>
         <v>FAIL</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -739,8 +770,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J9" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -771,8 +806,12 @@
         <f t="shared" si="2"/>
         <v>FAIL</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J10" t="str">
+        <f t="shared" si="3"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -803,8 +842,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J11" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -835,8 +878,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J12" t="str">
+        <f t="shared" si="3"/>
+        <v>B+</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -867,8 +914,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J13" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -899,8 +950,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J14" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -931,8 +986,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J15" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -963,8 +1022,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -995,8 +1058,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" t="str">
+        <f t="shared" si="3"/>
+        <v>A+</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1027,8 +1094,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1059,8 +1130,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1091,8 +1166,12 @@
         <f t="shared" si="2"/>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1122,6 +1201,10 @@
       <c r="I21" t="str">
         <f t="shared" si="2"/>
         <v>PASS</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="3"/>
+        <v>A</v>
       </c>
     </row>
   </sheetData>
